--- a/output/pdf_financials_xlsx/NTMC.xlsx
+++ b/output/pdf_financials_xlsx/NTMC.xlsx
@@ -1937,10 +1937,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.159999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.266244</v>
       </c>
     </row>
     <row r="93">
@@ -3253,7 +3253,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NTMC.xlsx
+++ b/output/pdf_financials_xlsx/NTMC.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.101484</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.036816</v>
       </c>
     </row>
     <row r="13">
@@ -882,10 +882,10 @@
         <v>-1.083347</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.303274</v>
+        <v>-7.404758</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.540135</v>
+        <v>-0.576951</v>
       </c>
     </row>
     <row r="28">
@@ -914,10 +914,10 @@
         <v>-1.083347</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.303274</v>
+        <v>-7.404758</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.540135</v>
+        <v>-0.576951</v>
       </c>
     </row>
     <row r="30">
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.127107</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.843559</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.862444</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.127107</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.843559</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.862444</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.157336</v>
+        <v>0.030229</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.161739</v>
+        <v>0.31818</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.988252</v>
+        <v>0.125808</v>
       </c>
     </row>
     <row r="49">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -3015,7 +3015,11 @@
           <t>Reclamation deposit (Note 8)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -3876,7 +3880,11 @@
           <t>Placement of reclamation deposit</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -4922,7 +4930,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">

--- a/output/pdf_financials_xlsx/NTMC.xlsx
+++ b/output/pdf_financials_xlsx/NTMC.xlsx
@@ -4347,7 +4347,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
